--- a/site/Integration-Configurations-Reference-Guide/headings.xlsx
+++ b/site/Integration-Configurations-Reference-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,7 +1409,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Import Limit</t>
+          <t>Incremental Mode</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,19 +1419,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01K58JHXX6Z2HTAV55K7M925WX</t>
+          <t>h_01KKTYBF06CSBK5A2AJN3HWFXP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58JHXX6Z2HTAV55K7M925WX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01KKTYBF06CSBK5A2AJN3HWFXP</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Update Limit</t>
+          <t>Incremental Mode Timestamp</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01K58JJ1N5B2A0FGEAPCZFYZ01</t>
+          <t>h_01KKTYBN3BW5P8S6E41R2HRG7T</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58JJ1N5B2A0FGEAPCZFYZ01</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01KKTYBN3BW5P8S6E41R2HRG7T</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Source Caching</t>
+          <t>Report Only</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,19 +1463,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
+          <t>h_01KKTY7RFXJK2DWK3DRV6GT4KG</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01KKTY7RFXJK2DWK3DRV6GT4KG</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Target Caching</t>
+          <t>Allow Creation of Inactive Users</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01K58XFVAP0BBF0GPYFKGANTV8</t>
+          <t>h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAP0BBF0GPYFKGANTV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Allow Creation of Inactive Users</t>
+          <t>Import Limit</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,41 +1507,41 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
+          <t>h_01K58JHXX6Z2HTAV55K7M925WX</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58JHXX6Z2HTAV55K7M925WX</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Update Limit</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01K58M5M642N07HGFF4BGYYJSB</t>
+          <t>h_01K58JJ1N5B2A0FGEAPCZFYZ01</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58M5M642N07HGFF4BGYYJSB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58JJ1N5B2A0FGEAPCZFYZ01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Report Mode</t>
+          <t>Source Caching</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,19 +1551,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01K58M5YKDTY2D8NQSS0D522RH</t>
+          <t>h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#01K58M5YKDTY2D8NQSS0D522RH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Email From Address</t>
+          <t>Target Caching</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,41 +1573,41 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01K58M5YKE0TB613KCAN1XYP4Q</t>
+          <t>h_01K58XFVAP0BBF0GPYFKGANTV8</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#01K58M5YKE0TB613KCAN1XYP4Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAP0BBF0GPYFKGANTV8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Send Reports</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQQGFA75V649HTX2Q0</t>
+          <t>h_01K58M5M642N07HGFF4BGYYJSB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQQGFA75V649HTX2Q0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58M5M642N07HGFF4BGYYJSB</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>To</t>
+          <t>Report Mode</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1617,19 +1617,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQ87D29WZXH2JRSV6E</t>
+          <t>01K58M5YKDTY2D8NQSS0D522RH</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQ87D29WZXH2JRSV6E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#01K58M5YKDTY2D8NQSS0D522RH</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Email From Address</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQDNPXC5FHD2J8ZXME</t>
+          <t>01K58M5YKE0TB613KCAN1XYP4Q</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQDNPXC5FHD2J8ZXME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#01K58M5YKE0TB613KCAN1XYP4Q</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Send On</t>
+          <t>Send Reports</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQZ34103Z4HBTFE29B</t>
+          <t>h_01K58XFVAQQGFA75V649HTX2Q0</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQZ34103Z4HBTFE29B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQQGFA75V649HTX2Q0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Safeguard Email List</t>
+          <t>To</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1683,19 +1683,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQXSSG0ZYG9STYC063</t>
+          <t>h_01K58XFVAQ87D29WZXH2JRSV6E</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQXSSG0ZYG9STYC063</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQ87D29WZXH2JRSV6E</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Send Details</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,32 +1705,98 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQVABFWM19KJXDKVFZ</t>
+          <t>h_01K58XFVAQDNPXC5FHD2J8ZXME</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQVABFWM19KJXDKVFZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQDNPXC5FHD2J8ZXME</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Send On</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>h_01K58XFVAQZ34103Z4HBTFE29B</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQZ34103Z4HBTFE29B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Safeguard Email List</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>h_01K58XFVAQXSSG0ZYG9STYC063</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQXSSG0ZYG9STYC063</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Send Details</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>h_01K58XFVAQVABFWM19KJXDKVFZ</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQVABFWM19KJXDKVFZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Send CSV Report</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>h_01K58XFVAQCGB6H2XZXN0KQ6MD</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01K58XFVAQCGB6H2XZXN0KQ6MD</t>
         </is>

--- a/site/Integration-Configurations-Reference-Guide/headings.xlsx
+++ b/site/Integration-Configurations-Reference-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,6 +1802,72 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Dashboard Insights</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>h_01KM274GVJ6BXEG2BQ609KGJ8J</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01KM274GVJ6BXEG2BQ609KGJ8J</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Monitor Provisioning</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>h_01KM272YSX744Y0S9Q181YBPRC</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01KM272YSX744Y0S9Q181YBPRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Enable Monitoring</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>h_01KM27D94ZAM5HS7P7PKF36ZZ7</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Configurations-Reference-Guide/#h_01KM27D94ZAM5HS7P7PKF36ZZ7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Integration-Configurations-Reference-Guide/headings.xlsx
+++ b/site/Integration-Configurations-Reference-Guide/headings.xlsx
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>User Match Expression</t>
+          <t>User / Source Match Expression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
